--- a/Convert_from_xlsx_to_Json/table_normalization/food-table02.xlsx
+++ b/Convert_from_xlsx_to_Json/table_normalization/food-table02.xlsx
@@ -103,8 +103,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="2">
-    <numFmt numFmtId="168" formatCode="[$-10409]#,###"/>
-    <numFmt numFmtId="169" formatCode="[$-10409]#,###.0"/>
+    <numFmt numFmtId="164" formatCode="[$-10409]#,###"/>
+    <numFmt numFmtId="165" formatCode="[$-10409]#,###.0"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -296,43 +296,73 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -348,51 +378,21 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
@@ -886,89 +886,89 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" s="1" customFormat="1" ht="15" customHeight="1">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="23" t="s">
+      <c r="B1" s="23"/>
+      <c r="C1" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="25" t="s">
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="26" t="s">
+      <c r="H1" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="I1" s="26" t="s">
+      <c r="I1" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="26" t="s">
+      <c r="J1" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="K1" s="26" t="s">
+      <c r="K1" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="L1" s="26" t="s">
+      <c r="L1" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="M1" s="27" t="s">
+      <c r="M1" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="N1" s="28" t="s">
+      <c r="N1" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="O1" s="22"/>
-      <c r="P1" s="22"/>
+      <c r="O1" s="23"/>
+      <c r="P1" s="23"/>
     </row>
     <row r="2" spans="1:16" s="1" customFormat="1" ht="50" customHeight="1">
-      <c r="A2" s="29"/>
-      <c r="B2" s="29"/>
-      <c r="C2" s="30" t="s">
+      <c r="A2" s="24"/>
+      <c r="B2" s="24"/>
+      <c r="C2" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="30" t="s">
+      <c r="D2" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="31" t="s">
+      <c r="E2" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="32"/>
-      <c r="G2" s="33" t="s">
+      <c r="F2" s="35"/>
+      <c r="G2" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="34" t="s">
+      <c r="H2" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="34" t="s">
+      <c r="I2" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="34" t="s">
+      <c r="J2" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="34" t="s">
+      <c r="K2" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="L2" s="34" t="s">
+      <c r="L2" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="M2" s="35" t="s">
+      <c r="M2" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="N2" s="36" t="s">
+      <c r="N2" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="O2" s="30" t="s">
+      <c r="O2" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="P2" s="30" t="s">
+      <c r="P2" s="17" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:16" s="1" customFormat="1">
-      <c r="A3" s="18">
+      <c r="A3" s="28">
         <v>2020</v>
       </c>
       <c r="B3" s="3" t="s">
@@ -980,10 +980,10 @@
       <c r="D3" s="4">
         <v>26.432500000000001</v>
       </c>
-      <c r="E3" s="14">
+      <c r="E3" s="36">
         <v>6957.3325000000004</v>
       </c>
-      <c r="F3" s="14"/>
+      <c r="F3" s="36"/>
       <c r="G3" s="5">
         <v>642.11199999999997</v>
       </c>
@@ -1016,7 +1016,7 @@
       </c>
     </row>
     <row r="4" spans="1:16" s="1" customFormat="1">
-      <c r="A4" s="19"/>
+      <c r="A4" s="29"/>
       <c r="B4" s="6" t="s">
         <v>18</v>
       </c>
@@ -1026,10 +1026,10 @@
       <c r="D4" s="5">
         <v>8.6311</v>
       </c>
-      <c r="E4" s="15">
+      <c r="E4" s="25">
         <v>6067.2311</v>
       </c>
-      <c r="F4" s="15"/>
+      <c r="F4" s="25"/>
       <c r="G4" s="5">
         <v>670.46</v>
       </c>
@@ -1062,7 +1062,7 @@
       </c>
     </row>
     <row r="5" spans="1:16" s="1" customFormat="1">
-      <c r="A5" s="19"/>
+      <c r="A5" s="29"/>
       <c r="B5" s="6" t="s">
         <v>19</v>
       </c>
@@ -1072,10 +1072,10 @@
       <c r="D5" s="5">
         <v>8.6311</v>
       </c>
-      <c r="E5" s="15">
+      <c r="E5" s="25">
         <v>7123.9310999999998</v>
       </c>
-      <c r="F5" s="15"/>
+      <c r="F5" s="25"/>
       <c r="G5" s="5">
         <v>572.60900000000004</v>
       </c>
@@ -1108,7 +1108,7 @@
       </c>
     </row>
     <row r="6" spans="1:16" s="1" customFormat="1">
-      <c r="A6" s="19"/>
+      <c r="A6" s="29"/>
       <c r="B6" s="6" t="s">
         <v>20</v>
       </c>
@@ -1118,10 +1118,10 @@
       <c r="D6" s="5">
         <v>26.205200000000001</v>
       </c>
-      <c r="E6" s="15">
+      <c r="E6" s="25">
         <v>7095.1052</v>
       </c>
-      <c r="F6" s="15"/>
+      <c r="F6" s="25"/>
       <c r="G6" s="5">
         <v>617.05200000000002</v>
       </c>
@@ -1154,7 +1154,7 @@
       </c>
     </row>
     <row r="7" spans="1:16" s="1" customFormat="1">
-      <c r="A7" s="19"/>
+      <c r="A7" s="29"/>
       <c r="B7" s="6" t="s">
         <v>21</v>
       </c>
@@ -1164,10 +1164,10 @@
       <c r="D7" s="5">
         <v>69.900000000000006</v>
       </c>
-      <c r="E7" s="15">
+      <c r="E7" s="25">
         <v>27243.599999999999</v>
       </c>
-      <c r="F7" s="15"/>
+      <c r="F7" s="25"/>
       <c r="G7" s="5">
         <v>642.11199999999997</v>
       </c>
@@ -1200,7 +1200,7 @@
       </c>
     </row>
     <row r="8" spans="1:16" s="1" customFormat="1">
-      <c r="A8" s="19">
+      <c r="A8" s="29">
         <v>2021</v>
       </c>
       <c r="B8" s="6" t="s">
@@ -1212,10 +1212,10 @@
       <c r="D8" s="5">
         <v>25.566199999999998</v>
       </c>
-      <c r="E8" s="15">
+      <c r="E8" s="25">
         <v>6925.2662</v>
       </c>
-      <c r="F8" s="15"/>
+      <c r="F8" s="25"/>
       <c r="G8" s="5">
         <v>715.654</v>
       </c>
@@ -1248,7 +1248,7 @@
       </c>
     </row>
     <row r="9" spans="1:16" s="1" customFormat="1">
-      <c r="A9" s="19"/>
+      <c r="A9" s="29"/>
       <c r="B9" s="6" t="s">
         <v>18</v>
       </c>
@@ -1258,10 +1258,10 @@
       <c r="D9" s="5">
         <v>8.3493999999999993</v>
       </c>
-      <c r="E9" s="15">
+      <c r="E9" s="25">
         <v>6971.5493999999999</v>
       </c>
-      <c r="F9" s="15"/>
+      <c r="F9" s="25"/>
       <c r="G9" s="5">
         <v>645.22799999999995</v>
       </c>
@@ -1294,7 +1294,7 @@
       </c>
     </row>
     <row r="10" spans="1:16" s="1" customFormat="1">
-      <c r="A10" s="19"/>
+      <c r="A10" s="29"/>
       <c r="B10" s="6" t="s">
         <v>19</v>
       </c>
@@ -1304,10 +1304,10 @@
       <c r="D10" s="5">
         <v>8.3493999999999993</v>
       </c>
-      <c r="E10" s="15">
+      <c r="E10" s="25">
         <v>6987.5493999999999</v>
       </c>
-      <c r="F10" s="15"/>
+      <c r="F10" s="25"/>
       <c r="G10" s="5">
         <v>535.42399999999998</v>
       </c>
@@ -1340,7 +1340,7 @@
       </c>
     </row>
     <row r="11" spans="1:16" s="1" customFormat="1">
-      <c r="A11" s="19"/>
+      <c r="A11" s="29"/>
       <c r="B11" s="6" t="s">
         <v>20</v>
       </c>
@@ -1350,10 +1350,10 @@
       <c r="D11" s="5">
         <v>25.335000000000001</v>
       </c>
-      <c r="E11" s="15">
+      <c r="E11" s="25">
         <v>7131.4350000000004</v>
       </c>
-      <c r="F11" s="15"/>
+      <c r="F11" s="25"/>
       <c r="G11" s="5">
         <v>585.14599999999996</v>
       </c>
@@ -1386,7 +1386,7 @@
       </c>
     </row>
     <row r="12" spans="1:16" s="1" customFormat="1">
-      <c r="A12" s="19"/>
+      <c r="A12" s="29"/>
       <c r="B12" s="6" t="s">
         <v>21</v>
       </c>
@@ -1396,10 +1396,10 @@
       <c r="D12" s="5">
         <v>67.599999999999994</v>
       </c>
-      <c r="E12" s="15">
+      <c r="E12" s="25">
         <v>28015.8</v>
       </c>
-      <c r="F12" s="15"/>
+      <c r="F12" s="25"/>
       <c r="G12" s="5">
         <v>715.654</v>
       </c>
@@ -1432,7 +1432,7 @@
       </c>
     </row>
     <row r="13" spans="1:16" s="1" customFormat="1">
-      <c r="A13" s="19">
+      <c r="A13" s="29">
         <v>2022</v>
       </c>
       <c r="B13" s="6" t="s">
@@ -1444,10 +1444,10 @@
       <c r="D13" s="5">
         <v>25.5472</v>
       </c>
-      <c r="E13" s="15">
+      <c r="E13" s="25">
         <v>7048.8472000000002</v>
       </c>
-      <c r="F13" s="15"/>
+      <c r="F13" s="25"/>
       <c r="G13" s="5">
         <v>675.577</v>
       </c>
@@ -1480,7 +1480,7 @@
       </c>
     </row>
     <row r="14" spans="1:16" s="1" customFormat="1">
-      <c r="A14" s="19"/>
+      <c r="A14" s="29"/>
       <c r="B14" s="6" t="s">
         <v>18</v>
       </c>
@@ -1490,10 +1490,10 @@
       <c r="D14" s="5">
         <v>8.3719999999999999</v>
       </c>
-      <c r="E14" s="15">
+      <c r="E14" s="25">
         <v>7079.9719999999998</v>
       </c>
-      <c r="F14" s="15"/>
+      <c r="F14" s="25"/>
       <c r="G14" s="5">
         <v>710.96</v>
       </c>
@@ -1526,7 +1526,7 @@
       </c>
     </row>
     <row r="15" spans="1:16" s="1" customFormat="1">
-      <c r="A15" s="19"/>
+      <c r="A15" s="29"/>
       <c r="B15" s="6" t="s">
         <v>19</v>
       </c>
@@ -1536,10 +1536,10 @@
       <c r="D15" s="5">
         <v>8.3719999999999999</v>
       </c>
-      <c r="E15" s="15">
+      <c r="E15" s="25">
         <v>7152.2719999999999</v>
       </c>
-      <c r="F15" s="15"/>
+      <c r="F15" s="25"/>
       <c r="G15" s="5">
         <v>685.62400000000002</v>
       </c>
@@ -1572,7 +1572,7 @@
       </c>
     </row>
     <row r="16" spans="1:16" s="1" customFormat="1">
-      <c r="A16" s="19"/>
+      <c r="A16" s="29"/>
       <c r="B16" s="6" t="s">
         <v>20</v>
       </c>
@@ -1582,10 +1582,10 @@
       <c r="D16" s="5">
         <v>25.308900000000001</v>
       </c>
-      <c r="E16" s="15">
+      <c r="E16" s="25">
         <v>7077.2088999999996</v>
       </c>
-      <c r="F16" s="15"/>
+      <c r="F16" s="25"/>
       <c r="G16" s="5">
         <v>696.53599999999994</v>
       </c>
@@ -1618,7 +1618,7 @@
       </c>
     </row>
     <row r="17" spans="1:16" s="1" customFormat="1">
-      <c r="A17" s="19"/>
+      <c r="A17" s="29"/>
       <c r="B17" s="6" t="s">
         <v>21</v>
       </c>
@@ -1628,10 +1628,10 @@
       <c r="D17" s="5">
         <v>67.599999999999994</v>
       </c>
-      <c r="E17" s="15">
+      <c r="E17" s="25">
         <v>28358.3</v>
       </c>
-      <c r="F17" s="15"/>
+      <c r="F17" s="25"/>
       <c r="G17" s="5">
         <v>675.577</v>
       </c>
@@ -1664,7 +1664,7 @@
       </c>
     </row>
     <row r="18" spans="1:16" s="1" customFormat="1">
-      <c r="A18" s="19">
+      <c r="A18" s="29">
         <v>2023</v>
       </c>
       <c r="B18" s="6" t="s">
@@ -1676,10 +1676,10 @@
       <c r="D18" s="5">
         <v>25.241099999999999</v>
       </c>
-      <c r="E18" s="15">
+      <c r="E18" s="25">
         <v>6849.1410999999998</v>
       </c>
-      <c r="F18" s="15"/>
+      <c r="F18" s="25"/>
       <c r="G18" s="5">
         <v>723.31600000000003</v>
       </c>
@@ -1712,7 +1712,7 @@
       </c>
     </row>
     <row r="19" spans="1:16" s="1" customFormat="1">
-      <c r="A19" s="19"/>
+      <c r="A19" s="29"/>
       <c r="B19" s="6" t="s">
         <v>18</v>
       </c>
@@ -1722,10 +1722,10 @@
       <c r="D19" s="5">
         <v>8.2768999999999995</v>
       </c>
-      <c r="E19" s="15">
+      <c r="E19" s="25">
         <v>6720.4768999999997</v>
       </c>
-      <c r="F19" s="15"/>
+      <c r="F19" s="25"/>
       <c r="G19" s="5">
         <v>633.53399999999999</v>
       </c>
@@ -1758,7 +1758,7 @@
       </c>
     </row>
     <row r="20" spans="1:16" s="1" customFormat="1">
-      <c r="A20" s="19"/>
+      <c r="A20" s="29"/>
       <c r="B20" s="6" t="s">
         <v>19</v>
       </c>
@@ -1768,10 +1768,10 @@
       <c r="D20" s="5">
         <v>8.2768999999999995</v>
       </c>
-      <c r="E20" s="15">
+      <c r="E20" s="25">
         <v>6629.7768999999998</v>
       </c>
-      <c r="F20" s="15"/>
+      <c r="F20" s="25"/>
       <c r="G20" s="5">
         <v>545.57299999999998</v>
       </c>
@@ -1804,7 +1804,7 @@
       </c>
     </row>
     <row r="21" spans="1:16" s="1" customFormat="1">
-      <c r="A21" s="19"/>
+      <c r="A21" s="29"/>
       <c r="B21" s="6" t="s">
         <v>20</v>
       </c>
@@ -1814,10 +1814,10 @@
       <c r="D21" s="5">
         <v>25.005099999999999</v>
       </c>
-      <c r="E21" s="15">
+      <c r="E21" s="25">
         <v>6834.5051000000003</v>
       </c>
-      <c r="F21" s="15"/>
+      <c r="F21" s="25"/>
       <c r="G21" s="5">
         <v>558.16</v>
       </c>
@@ -1850,7 +1850,7 @@
       </c>
     </row>
     <row r="22" spans="1:16" s="1" customFormat="1">
-      <c r="A22" s="20"/>
+      <c r="A22" s="30"/>
       <c r="B22" s="2" t="s">
         <v>21</v>
       </c>
@@ -1860,10 +1860,10 @@
       <c r="D22" s="7">
         <v>66.8</v>
       </c>
-      <c r="E22" s="16">
+      <c r="E22" s="26">
         <v>27033.9</v>
       </c>
-      <c r="F22" s="17"/>
+      <c r="F22" s="27"/>
       <c r="G22" s="7">
         <v>723.31600000000003</v>
       </c>
@@ -1897,6 +1897,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="N1:P1"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E9:F9"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="E20:F20"/>
     <mergeCell ref="E21:F21"/>
@@ -1913,18 +1925,6 @@
     <mergeCell ref="E10:F10"/>
     <mergeCell ref="E11:F11"/>
     <mergeCell ref="E12:F12"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="C1:F1"/>
-    <mergeCell ref="N1:P1"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="E4:F4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.5" top="1" bottom="0.75" header="1" footer="0.75"/>
   <pageSetup orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
